--- a/data/trans_orig/IP1013-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP1013-Clase-trans_orig.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3085</t>
+          <t>3550</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4049</t>
+          <t>3381</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4097</t>
+          <t>4612</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,28%</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>101267</t>
+          <t>100802</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>93496</t>
+          <t>94164</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>197801</t>
+          <t>197286</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3235</t>
+          <t>3218</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2998</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,75%</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>197498</t>
+          <t>197515</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>399809</t>
+          <t>399770</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4001</t>
+          <t>4386</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3841</t>
+          <t>2705</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5283</t>
+          <t>6130</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,46%</t>
         </is>
       </c>
     </row>
@@ -2903,7 +2903,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>634855</t>
+          <t>634470</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2938,7 +2938,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>680762</t>
+          <t>681898</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2973,7 +2973,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1318176</t>
+          <t>1317329</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -2988,7 +2988,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3372,7 +3372,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3280</t>
+          <t>3302</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3843</t>
+          <t>3565</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>85159</t>
+          <t>85137</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>174360</t>
+          <t>174638</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4380</t>
+          <t>4352</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4436,7 +4436,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4471</t>
+          <t>3971</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>686</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6753</t>
+          <t>6752</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4509,7 +4509,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>201248</t>
+          <t>201276</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -4544,7 +4544,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>222393</t>
+          <t>222893</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -4559,7 +4559,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>425739</t>
+          <t>425740</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>431804</t>
+          <t>431806</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4779,7 +4779,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4462</t>
+          <t>3487</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4794,7 +4794,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4122</t>
+          <t>3453</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4829,7 +4829,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -4887,7 +4887,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>135372</t>
+          <t>136347</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -4902,7 +4902,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4922,7 +4922,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>284881</t>
+          <t>285550</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -4937,7 +4937,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>662</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6112</t>
+          <t>5777</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5445,7 +5445,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5465,7 +5465,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5390</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5480,7 +5480,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1413</t>
+          <t>1919</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>8203</t>
+          <t>8691</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,63%</t>
         </is>
       </c>
     </row>
@@ -5538,12 +5538,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>667969</t>
+          <t>668304</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>673420</t>
+          <t>673419</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5553,7 +5553,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -5573,7 +5573,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>708111</t>
+          <t>708184</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1379379</t>
+          <t>1378891</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1386169</t>
+          <t>1385663</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,9%</t>
+          <t>99,86%</t>
         </is>
       </c>
     </row>
@@ -7374,12 +7374,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>594</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5414</t>
+          <t>6280</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7444,12 +7444,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6458</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7459,12 +7459,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -7487,12 +7487,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>130780</t>
+          <t>129914</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>135604</t>
+          <t>135600</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7557,12 +7557,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>272824</t>
+          <t>273884</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>278689</t>
+          <t>279282</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>100,0%</t>
         </is>
       </c>
     </row>
@@ -8060,82 +8060,82 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
+          <t>594</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>5746</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,31%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>0,86%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>2074</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
           <t>595</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>5658</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>0,84%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>2074</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>596</t>
-        </is>
-      </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5731</t>
+          <t>5708</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8173,12 +8173,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>665844</t>
+          <t>665756</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>670907</t>
+          <t>670908</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8188,7 +8188,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -8243,12 +8243,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1375508</t>
+          <t>1375531</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1380643</t>
+          <t>1380644</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">

--- a/data/trans_orig/IP1013-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP1013-Clase-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -727,102 +727,102 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>673</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4039</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,69%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>4,14%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>622</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3550</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3077</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,6%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3,4%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>673</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3381</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>2,95%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>1295</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>4576</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>3,47%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1295</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>4612</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -835,74 +835,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>96872</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>93506</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>97545</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>99,31%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>95,86%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>103730</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>100802</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>101275</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>104352</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>99,4%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>96,6%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>97,05%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>96872</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>94164</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>97545</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,31%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>96,53%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>297</t>
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>197286</t>
+          <t>197322</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>97545</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>97545</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>97545</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>153</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>104352</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>104352</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>104352</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>97545</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>97545</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>97545</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1183,42 +1183,42 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>85970</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
           <t>87389</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>85970</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1296,52 +1296,52 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>85970</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>85970</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>85970</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
           <t>87389</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>87389</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>87389</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>85970</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>85970</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>85970</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1521,47 +1521,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>99332</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>101</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>67392</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>99332</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>99332</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>99332</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>99332</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>101</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>67392</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>67392</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>67392</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>99332</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>99332</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>99332</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,107 +1751,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>642</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3218</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3228</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,32%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>1,6%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>1,61%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>3230</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>642</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>3037</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -1864,74 +1864,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>202074</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>302</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>200091</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>197515</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>197505</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>200733</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,68%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>98,4%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>98,39%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>304</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>202074</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>606</t>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>399770</t>
+          <t>399577</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>202074</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>202074</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>202074</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>303</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>200733</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>200733</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>200733</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>304</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>202074</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>202074</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>202074</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2207,47 +2207,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>127289</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>104120</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>127289</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>127289</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>127289</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>127289</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>104120</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>104120</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>104120</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>127289</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>127289</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>127289</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2550,47 +2550,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>72392</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>74870</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>72392</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2663,57 +2663,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>72392</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>72392</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>72392</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>74870</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>74870</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>74870</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>72392</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>72392</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>72392</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2780,74 +2780,74 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>673</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>3377</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,1%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>0,49%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>1264</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>4386</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>4429</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>0,2%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="P22" s="2" t="inlineStr">
         <is>
           <t>0,69%</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>673</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>2705</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,1%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
           <t>3</t>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6130</t>
+          <t>5177</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,39%</t>
         </is>
       </c>
     </row>
@@ -2893,74 +2893,74 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1028</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>683930</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>681226</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>684603</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>99,9%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>99,51%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>951</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>637592</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>634470</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>634427</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>638856</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>99,8%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
         <is>
           <t>99,31%</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="P23" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1028</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>683930</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>681898</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>684603</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>99,9%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>99,6%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>1979</t>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1317329</t>
+          <t>1318282</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -2988,7 +2988,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3006,57 +3006,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>1029</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>684603</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>684603</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>684603</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>953</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>638856</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>638856</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>638856</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>1029</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>684603</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>684603</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>684603</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3178,7 +3178,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3189,7 +3189,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3357,107 +3357,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>661</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3302</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3972</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,75%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3,73%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>4,49%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>661</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>3329</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>661</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3565</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -3470,74 +3470,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>89763</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>127</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>87778</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>85137</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>84467</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>88439</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>99,25%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>96,27%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>95,51%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>89763</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>257</t>
@@ -3550,7 +3550,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>174638</t>
+          <t>174874</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3583,57 +3583,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>89763</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>89763</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>89763</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>88439</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>88439</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>88439</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>89763</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>89763</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>89763</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3813,47 +3813,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>96111</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>135</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>92729</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>96111</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -3926,57 +3926,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>96111</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>96111</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>96111</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>135</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>92729</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>92729</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>92729</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>96111</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>96111</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>96111</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4156,47 +4156,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>86890</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>123</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>84205</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>86890</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -4269,57 +4269,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>86890</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>86890</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>86890</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>123</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>84205</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>84205</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>84205</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>86890</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>86890</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>86890</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4391,67 +4391,67 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>1292</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4009</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1,77%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>1415</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4352</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4919</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,69%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,12%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1292</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3971</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>686</t>
+          <t>673</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6752</t>
+          <t>6449</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,49%</t>
         </is>
       </c>
     </row>
@@ -4499,74 +4499,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>225572</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>222855</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>226864</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,43%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>98,23%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>296</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>204213</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>201276</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>200709</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>205628</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,31%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>97,88%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>97,61%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>320</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>225572</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>222893</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>226864</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,43%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>98,25%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>616</t>
@@ -4579,12 +4579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>425740</t>
+          <t>426043</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>431806</t>
+          <t>431819</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4612,57 +4612,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>226864</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>226864</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>226864</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>298</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>205628</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>205628</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>205628</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>322</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>226864</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>226864</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>226864</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4729,107 +4729,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>687</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3441</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
+          <t>0,49%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>687</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>3487</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>3481</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,24%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>2,49%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>687</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>3453</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,24%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -4842,72 +4842,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>139147</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>136393</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>139834</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,51%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>97,54%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>213</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>149169</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>139147</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>136347</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>139834</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,51%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4922,7 +4922,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>285550</t>
+          <t>285522</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -4937,7 +4937,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -4955,57 +4955,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>139834</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>139834</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>139834</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>213</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>149169</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>149169</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>149169</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>139834</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>139834</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>139834</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5185,47 +5185,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>74038</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>53911</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>74038</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -5298,57 +5298,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>74038</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>74038</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>74038</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>53911</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>53911</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>53911</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>74038</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>74038</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>74038</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5420,69 +5420,69 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
+          <t>1979</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>621</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>5251</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>0,74%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
           <t>2076</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>662</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>5777</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>660</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>5809</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>0,31%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>0,1%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="P22" s="2" t="inlineStr">
         <is>
           <t>0,86%</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>1979</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>620</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>5317</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
           <t>6</t>
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1919</t>
+          <t>1418</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>8691</t>
+          <t>9381</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,68%</t>
         </is>
       </c>
     </row>
@@ -5528,74 +5528,74 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1015</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>711522</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>708250</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>712880</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>99,72%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>99,26%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>99,91%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>970</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>672005</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>668304</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>673419</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>668272</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>673421</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>99,69%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
         <is>
           <t>99,14%</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="P23" s="2" t="inlineStr">
         <is>
           <t>99,9%</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1015</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>711522</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>708184</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>712881</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>99,72%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>99,25%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>99,91%</t>
-        </is>
-      </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>1985</t>
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1378891</t>
+          <t>1378201</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1385663</t>
+          <t>1386164</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,9%</t>
         </is>
       </c>
     </row>
@@ -5641,57 +5641,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>1018</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>713501</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>713501</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>713501</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>973</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>674081</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>674081</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>674081</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>1018</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>713501</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>713501</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>713501</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -5813,7 +5813,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5824,7 +5824,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6105,47 +6105,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>99797</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>126</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>83090</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>99797</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -6218,57 +6218,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>99797</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>99797</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>99797</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>126</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>83090</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>83090</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>83090</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>99797</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>99797</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>99797</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6448,47 +6448,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>112746</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>105714</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>112746</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -6561,57 +6561,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>112746</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>112746</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>112746</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>105714</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>105714</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>105714</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>112746</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>112746</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>112746</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6791,47 +6791,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>75428</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>61840</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>75428</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -6904,57 +6904,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>75428</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>75428</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>75428</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>61840</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>61840</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>61840</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>75428</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>75428</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>75428</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7134,47 +7134,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>210854</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>341</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>223577</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>301</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>210854</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -7247,57 +7247,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>210854</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>210854</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>210854</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>341</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>223577</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>223577</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>223577</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>301</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>210854</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>210854</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>210854</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7364,72 +7364,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>2074</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>594</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>6280</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>579</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>5898</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>1,52%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>4,61%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7444,12 +7444,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>598</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>5736</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7459,12 +7459,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -7477,72 +7477,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>143088</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>203</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>134120</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>129914</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>135600</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>130296</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>135615</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>98,48%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>95,39%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>99,56%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>143088</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7557,12 +7557,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>273884</t>
+          <t>273546</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>279282</t>
+          <t>278684</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,79%</t>
         </is>
       </c>
     </row>
@@ -7590,57 +7590,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>143088</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>143088</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>143088</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>206</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>136194</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>136194</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>136194</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>143088</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>143088</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>143088</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7820,47 +7820,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>67825</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>61087</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>67825</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -7933,57 +7933,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>67825</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>67825</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>67825</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>61087</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>61087</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>61087</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>67825</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>67825</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>67825</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8050,72 +8050,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>2074</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>594</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>5746</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>593</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>5712</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>0,31%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>0,09%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>597</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5708</t>
+          <t>5957</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,43%</t>
         </is>
       </c>
     </row>
@@ -8163,74 +8163,74 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1017</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>709737</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>1010</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>669428</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>665756</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>670908</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>665790</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>670909</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>99,69%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>99,14%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>99,15%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
         <is>
           <t>99,91%</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1017</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>709737</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>2027</t>
@@ -8243,12 +8243,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1375531</t>
+          <t>1375282</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1380644</t>
+          <t>1380642</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8258,7 +8258,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -8276,57 +8276,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>1017</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>709737</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>709737</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>709737</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>1013</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>671502</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>671502</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>671502</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>1017</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>709737</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>709737</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>709737</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
